--- a/research/traditional_assets/database/data/sweden/sweden_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1317776252573782</v>
+        <v>0.1979057591623037</v>
       </c>
       <c r="H2">
-        <v>0.1317776252573782</v>
+        <v>0.1979057591623037</v>
       </c>
       <c r="I2">
-        <v>0.1520418668496911</v>
+        <v>0.1078534031413613</v>
       </c>
       <c r="J2">
-        <v>0.133429845218091</v>
+        <v>0.08521075156908767</v>
       </c>
       <c r="K2">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="L2">
-        <v>0.06666094715168154</v>
+        <v>0.08157068062827225</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,16 +627,22 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>66</v>
+        <v>58.5</v>
       </c>
       <c r="V2">
-        <v>0.4625087596355991</v>
+        <v>0.4631828978622328</v>
+      </c>
+      <c r="W2">
+        <v>0.226453488372093</v>
       </c>
       <c r="X2">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
+      </c>
+      <c r="Y2">
+        <v>0.1514596194142164</v>
       </c>
       <c r="AB2">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-66</v>
+        <v>-58.5</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,28 +663,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.860495436766623</v>
+        <v>-0.8628318584070797</v>
       </c>
       <c r="AK2">
-        <v>2.088607594936709</v>
+        <v>2.48936170212766</v>
       </c>
       <c r="AL2">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="AM2">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>1107.625</v>
+        <v>396.1538461538462</v>
       </c>
       <c r="AP2">
-        <v>84.83290488431876</v>
+        <v>-5.223214285714286</v>
       </c>
       <c r="AQ2">
-        <v>1107.625</v>
+        <v>396.1538461538462</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1381407471763684</v>
+        <v>0.1979057591623037</v>
       </c>
       <c r="H3">
-        <v>0.1381407471763684</v>
+        <v>0.1979057591623037</v>
       </c>
       <c r="I3">
-        <v>0.1624674196350999</v>
+        <v>0.1078534031413613</v>
       </c>
       <c r="J3">
-        <v>0.1226909134485755</v>
+        <v>0.08521075156908767</v>
       </c>
       <c r="K3">
-        <v>8.75</v>
+        <v>7.79</v>
       </c>
       <c r="L3">
-        <v>0.07602085143353605</v>
+        <v>0.08157068062827225</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,16 +743,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>66</v>
+        <v>58.5</v>
       </c>
       <c r="V3">
-        <v>0.5080831408775981</v>
+        <v>0.4631828978622328</v>
+      </c>
+      <c r="W3">
+        <v>0.226453488372093</v>
       </c>
       <c r="X3">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
+      </c>
+      <c r="Y3">
+        <v>0.1514596194142164</v>
       </c>
       <c r="AB3">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -758,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-66</v>
+        <v>-58.5</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -767,126 +779,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.032863849765258</v>
+        <v>-0.8628318584070797</v>
       </c>
       <c r="AK3">
-        <v>2.088607594936709</v>
+        <v>2.48936170212766</v>
       </c>
       <c r="AL3">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="AM3">
-        <v>0.015</v>
+        <v>0.026</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>1246.666666666667</v>
+        <v>396.1538461538462</v>
+      </c>
+      <c r="AP3">
+        <v>-5.223214285714286</v>
       </c>
       <c r="AQ3">
-        <v>1246.666666666667</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Paydrive AB (publ) (NGM:PYDR)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-0.3698630136986302</v>
-      </c>
-      <c r="H4">
-        <v>-0.3698630136986302</v>
-      </c>
-      <c r="I4">
-        <v>-0.6698630136986301</v>
-      </c>
-      <c r="J4">
-        <v>-0.6698630136986301</v>
-      </c>
-      <c r="K4">
-        <v>-0.98</v>
-      </c>
-      <c r="L4">
-        <v>-0.6712328767123288</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.04381734796752063</v>
-      </c>
-      <c r="AB4">
-        <v>0.04381734796752063</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0.001</v>
-      </c>
-      <c r="AM4">
-        <v>0.001</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AO4">
-        <v>-978</v>
-      </c>
-      <c r="AP4">
-        <v>-0</v>
-      </c>
-      <c r="AQ4">
-        <v>-978</v>
+        <v>396.1538461538462</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_insurance_general.xlsx
@@ -588,61 +588,64 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1979057591623037</v>
+        <v>0.1261510128913444</v>
       </c>
       <c r="H2">
-        <v>0.1979057591623037</v>
+        <v>0.1261510128913444</v>
       </c>
       <c r="I2">
-        <v>0.1078534031413613</v>
+        <v>0.1823204419889503</v>
       </c>
       <c r="J2">
-        <v>0.08521075156908767</v>
+        <v>0.1439226519337017</v>
       </c>
       <c r="K2">
-        <v>7.79</v>
+        <v>15.7</v>
       </c>
       <c r="L2">
-        <v>0.08157068062827225</v>
+        <v>0.1445672191528545</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.100494233937397</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.7770700636942675</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03871499176276771</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.2993630573248408</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>7.499999999999999</v>
+      </c>
+      <c r="T2">
+        <v>0.6147540983606558</v>
       </c>
       <c r="U2">
-        <v>58.5</v>
+        <v>36.7</v>
       </c>
       <c r="V2">
-        <v>0.4631828978622328</v>
+        <v>0.3023064250411862</v>
       </c>
       <c r="W2">
-        <v>0.226453488372093</v>
+        <v>0.4485714285714286</v>
       </c>
       <c r="X2">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="Y2">
-        <v>0.1514596194142164</v>
+        <v>0.3811376081949118</v>
       </c>
       <c r="AB2">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -654,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-58.5</v>
+        <v>-36.7</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -663,28 +666,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.8628318584070797</v>
+        <v>-0.4332939787485242</v>
       </c>
       <c r="AK2">
-        <v>2.48936170212766</v>
+        <v>-14.68</v>
       </c>
       <c r="AL2">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="AM2">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>396.1538461538462</v>
+        <v>638.7096774193549</v>
       </c>
       <c r="AP2">
-        <v>-5.223214285714286</v>
+        <v>-1.816831683168317</v>
       </c>
       <c r="AQ2">
-        <v>396.1538461538462</v>
+        <v>638.7096774193549</v>
       </c>
     </row>
     <row r="3">
@@ -704,61 +707,64 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1979057591623037</v>
+        <v>0.1261510128913444</v>
       </c>
       <c r="H3">
-        <v>0.1979057591623037</v>
+        <v>0.1261510128913444</v>
       </c>
       <c r="I3">
-        <v>0.1078534031413613</v>
+        <v>0.1823204419889503</v>
       </c>
       <c r="J3">
-        <v>0.08521075156908767</v>
+        <v>0.1439226519337017</v>
       </c>
       <c r="K3">
-        <v>7.79</v>
+        <v>15.7</v>
       </c>
       <c r="L3">
-        <v>0.08157068062827225</v>
+        <v>0.1445672191528545</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>12.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.100494233937397</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.7770700636942675</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>4.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03871499176276771</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2993630573248408</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.499999999999999</v>
+      </c>
+      <c r="T3">
+        <v>0.6147540983606558</v>
       </c>
       <c r="U3">
-        <v>58.5</v>
+        <v>36.7</v>
       </c>
       <c r="V3">
-        <v>0.4631828978622328</v>
+        <v>0.3023064250411862</v>
       </c>
       <c r="W3">
-        <v>0.226453488372093</v>
+        <v>0.4485714285714286</v>
       </c>
       <c r="X3">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="Y3">
-        <v>0.1514596194142164</v>
+        <v>0.3811376081949118</v>
       </c>
       <c r="AB3">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -770,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-58.5</v>
+        <v>-36.7</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -779,28 +785,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.8628318584070797</v>
+        <v>-0.4332939787485242</v>
       </c>
       <c r="AK3">
-        <v>2.48936170212766</v>
+        <v>-14.68</v>
       </c>
       <c r="AL3">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>396.1538461538462</v>
+        <v>638.7096774193549</v>
       </c>
       <c r="AP3">
-        <v>-5.223214285714286</v>
+        <v>-1.816831683168317</v>
       </c>
       <c r="AQ3">
-        <v>396.1538461538462</v>
+        <v>638.7096774193549</v>
       </c>
     </row>
   </sheetData>
